--- a/test_invoices/TEST_Customs_Bulk_10_customs.xlsx
+++ b/test_invoices/TEST_Customs_Bulk_10_customs.xlsx
@@ -1406,7 +1406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A4:M14"/>
+  <dimension ref="A4:S14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="4">
@@ -1457,22 +1457,52 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>HTS</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Duty Rate</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Sec 301</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Sec 232</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>Duty</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>MPF</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>HMF</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Brokerage</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>Amount</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Notes</t>
         </is>
       </c>
     </row>
@@ -1516,17 +1546,45 @@
       <c r="I5" t="n">
         <v>184500</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>9403.20.0090</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
         <v>46125</v>
       </c>
-      <c r="K5" t="n">
+      <c r="O5" t="n">
         <v>538.4</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>235.34</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
+        <v>285</v>
+      </c>
+      <c r="R5" t="n">
         <v>47313.74</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Garage cabinet — Pro 3.0 Series</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1569,18 +1627,42 @@
       <c r="I6" t="n">
         <v>22400</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>7321.11.6000</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>5.7%</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
         <v>6877.2</v>
       </c>
-      <c r="K6" t="n">
+      <c r="O6" t="n">
         <v>78.40000000000001</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>28.56</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
+        <v>175</v>
+      </c>
+      <c r="R6" t="n">
         <v>7259.16</v>
       </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1622,18 +1704,42 @@
       <c r="I7" t="n">
         <v>145200</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>9403.20.0090</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
         <v>36300</v>
       </c>
-      <c r="K7" t="n">
+      <c r="O7" t="n">
         <v>485</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>185.21</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
+        <v>285</v>
+      </c>
+      <c r="R7" t="n">
         <v>37385.21</v>
       </c>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1675,17 +1781,45 @@
       <c r="I8" t="n">
         <v>89750</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>7308.30.5050</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
         <v>67312.5</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
         <v>538.4</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>114.45</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
+        <v>285</v>
+      </c>
+      <c r="R8" t="n">
         <v>68380.35000000001</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>STEEL — Sec 232 applies on top of Sec 301</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1728,18 +1862,42 @@
       <c r="I9" t="n">
         <v>67300</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>9403.40.9080</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
         <v>16825</v>
       </c>
-      <c r="K9" t="n">
+      <c r="O9" t="n">
         <v>425</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>85.81999999999999</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
+        <v>225</v>
+      </c>
+      <c r="R9" t="n">
         <v>17670.82</v>
       </c>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1781,17 +1939,45 @@
       <c r="I10" t="n">
         <v>98500</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>7321.11.3000</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5.7%</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
         <v>30298.5</v>
       </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
         <v>538.4</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>125.62</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
+        <v>285</v>
+      </c>
+      <c r="R10" t="n">
         <v>31377.52</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>HS classification under review — possible 7321.11.6000 drift</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1834,18 +2020,42 @@
       <c r="I11" t="n">
         <v>54200</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>9403.10.0040</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
         <v>13550</v>
       </c>
-      <c r="K11" t="n">
+      <c r="O11" t="n">
         <v>345</v>
       </c>
-      <c r="L11" t="n">
+      <c r="P11" t="n">
         <v>69.15000000000001</v>
       </c>
-      <c r="M11" t="n">
+      <c r="Q11" t="n">
+        <v>225</v>
+      </c>
+      <c r="R11" t="n">
         <v>14299.15</v>
       </c>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,17 +2097,45 @@
       <c r="I12" t="n">
         <v>112800</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>7308.30.5050</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
         <v>84600</v>
       </c>
-      <c r="K12" t="n">
+      <c r="O12" t="n">
         <v>538.4</v>
       </c>
-      <c r="L12" t="n">
+      <c r="P12" t="n">
         <v>143.9</v>
       </c>
-      <c r="M12" t="n">
+      <c r="Q12" t="n">
+        <v>285</v>
+      </c>
+      <c r="R12" t="n">
         <v>85697.3</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>STEEL — Sec 232 applies</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1940,18 +2178,42 @@
       <c r="I13" t="n">
         <v>43100</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>9403.20.0090</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
         <v>10775</v>
       </c>
-      <c r="K13" t="n">
+      <c r="O13" t="n">
         <v>275</v>
       </c>
-      <c r="L13" t="n">
+      <c r="P13" t="n">
         <v>54.99</v>
       </c>
-      <c r="M13" t="n">
+      <c r="Q13" t="n">
+        <v>225</v>
+      </c>
+      <c r="R13" t="n">
         <v>11439.99</v>
       </c>
+      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1993,18 +2255,42 @@
       <c r="I14" t="n">
         <v>78900</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9403.20.0090</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
         <v>19725</v>
       </c>
-      <c r="K14" t="n">
+      <c r="O14" t="n">
         <v>502.85</v>
       </c>
-      <c r="L14" t="n">
+      <c r="P14" t="n">
         <v>100.66</v>
       </c>
-      <c r="M14" t="n">
+      <c r="Q14" t="n">
+        <v>225</v>
+      </c>
+      <c r="R14" t="n">
         <v>20663.51</v>
       </c>
+      <c r="S14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
